--- a/Problem4_Delinquency_Escalation_Loss_Severity/reports/financial_impact_reporting_packaging/AMEX_Problem4_Financial_Impact_Workbook.xlsx
+++ b/Problem4_Delinquency_Escalation_Loss_Severity/reports/financial_impact_reporting_packaging/AMEX_Problem4_Financial_Impact_Workbook.xlsx
@@ -20,10 +20,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="$#,##0;($#,##0);-"/>
+    <numFmt numFmtId="164" formatCode="$#,##0;($#,##0);-"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -75,6 +75,12 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="000B1F3A"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -121,15 +127,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -140,14 +146,25 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -700,7 +717,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:F13"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -710,6 +727,7 @@
     <col width="3" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -724,13 +742,20 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="B4" s="22" t="inlineStr">
+        <is>
+          <t>Project Portfolio Prepared By Nandagopal R</t>
+        </is>
+      </c>
+    </row>
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Total Loss -- Flat LGD</t>
         </is>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="16">
         <f>SUM('Tier Financial Detail'!F2:F4)</f>
         <v/>
       </c>
@@ -741,7 +766,7 @@
           <t>Total Loss -- Tier LGD</t>
         </is>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="16">
         <f>SUM('Tier Financial Detail'!G2:G4)</f>
         <v/>
       </c>
@@ -752,7 +777,7 @@
           <t>Loss Recognition Change</t>
         </is>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="17">
         <f>D6-D5</f>
         <v/>
       </c>
@@ -865,7 +890,7 @@
           <t>Ead Per Account Usd</t>
         </is>
       </c>
-      <c r="B2" s="10" t="n">
+      <c r="B2" s="18" t="n">
         <v>5000</v>
       </c>
       <c r="C2" s="11" t="inlineStr">
@@ -880,7 +905,7 @@
           <t>Baseline Flat Lgd</t>
         </is>
       </c>
-      <c r="B3" s="12" t="n">
+      <c r="B3" s="19" t="n">
         <v>0.45</v>
       </c>
       <c r="C3" s="11" t="inlineStr">
@@ -895,7 +920,7 @@
           <t>Severe Tier Intervention Success Rate</t>
         </is>
       </c>
-      <c r="B4" s="12" t="n">
+      <c r="B4" s="19" t="n">
         <v>0.15</v>
       </c>
       <c r="C4" s="11" t="inlineStr">
@@ -910,7 +935,7 @@
           <t>Implementation Cost Usd</t>
         </is>
       </c>
-      <c r="B5" s="10" t="n">
+      <c r="B5" s="18" t="n">
         <v>60000</v>
       </c>
       <c r="C5" s="11" t="inlineStr">
@@ -1009,17 +1034,17 @@
       <c r="C2" t="n">
         <v>407</v>
       </c>
-      <c r="D2" s="14" t="n">
+      <c r="D2" s="20" t="n">
         <v>0.01342</v>
       </c>
-      <c r="E2" s="14" t="n">
+      <c r="E2" s="20" t="n">
         <v>0.3015</v>
       </c>
-      <c r="F2" s="15">
+      <c r="F2" s="21">
         <f>C2*Assumptions!$B$2*Assumptions!$B$3</f>
         <v/>
       </c>
-      <c r="G2" s="15">
+      <c r="G2" s="21">
         <f>C2*Assumptions!$B$2*E2</f>
         <v/>
       </c>
@@ -1036,17 +1061,17 @@
       <c r="C3" t="n">
         <v>3422</v>
       </c>
-      <c r="D3" s="14" t="n">
+      <c r="D3" s="20" t="n">
         <v>0.110658</v>
       </c>
-      <c r="E3" s="14" t="n">
+      <c r="E3" s="20" t="n">
         <v>0.45</v>
       </c>
-      <c r="F3" s="15">
+      <c r="F3" s="21">
         <f>C3*Assumptions!$B$2*Assumptions!$B$3</f>
         <v/>
       </c>
-      <c r="G3" s="15">
+      <c r="G3" s="21">
         <f>C3*Assumptions!$B$2*E3</f>
         <v/>
       </c>
@@ -1063,17 +1088,17 @@
       <c r="C4" t="n">
         <v>19937</v>
       </c>
-      <c r="D4" s="14" t="n">
+      <c r="D4" s="20" t="n">
         <v>0.653008</v>
       </c>
-      <c r="E4" s="14" t="n">
+      <c r="E4" s="20" t="n">
         <v>0.648</v>
       </c>
-      <c r="F4" s="15">
+      <c r="F4" s="21">
         <f>C4*Assumptions!$B$2*Assumptions!$B$3</f>
         <v/>
       </c>
-      <c r="G4" s="15">
+      <c r="G4" s="21">
         <f>C4*Assumptions!$B$2*E4</f>
         <v/>
       </c>
